--- a/Thematic analysis sheets.xlsx
+++ b/Thematic analysis sheets.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MY UBI Courses\3rd semster\Thesis paper\Detailed Thesis\final Text Review\final papers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MY UBI Courses\3rd semster\final thesis UC 1\JSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B48191D-CF17-4FEB-BE41-F97079DB2084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977F3BD4-0752-494E-8249-0F04E1B85D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CED0FAB-A1DE-468A-89DF-AD8733700714}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$H$1:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$G$1:$G$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -468,12 +468,6 @@
     <t>gates</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1. Sandboxing: Execution isolation for tool use.
-        2. Trajectory Observability: Immutable audit logs of agent plans and actions.
-        3. Safety Ontologies: Structured hazard analysis.
-        4. Role-Based Access Control (RBAC): Limiting agent permissions.</t>
-  </si>
-  <si>
     <t>HumanEval benchmark and promotes trajectory-aware benchmarks that measure plans, costs, and tool invocations. It highlights SWE-bench (issue fixing) and HumanEvalComm (communication) as emerging standards.</t>
   </si>
   <si>
@@ -673,9 +667,6 @@
     <t>Quality assurance strategies for machine learning applications in big data analytics an overview</t>
   </si>
   <si>
-    <t>"Holistic Pipeline QA" (Testing the process, not just the artifact).</t>
-  </si>
-  <si>
     <t>Orchestrated Pipeline Integration" (System-level coordination)…. A clear distinction in coordination patterns is observed between 'Agentic Negotiation' (seen in Multi-Agent Systems) and 'Structural Orchestration' (seen in Industrial ML). As highlighted in the Quality Assurance survey, industrial systems primarily rely on Linear Pipelines where coordination is defined by rigid data flows. Here, the primary risk is not 'disagreement' between agents, but 'Feature Interaction Conflicts'—where correctly functioning components (e.g., voice and facial recognition) produce catastrophic failures when integrated, necessitating rigorous System Integration Testing rather than social consensus mechanisms."</t>
   </si>
   <si>
@@ -893,12 +884,21 @@
   <si>
     <t>HELM benchmark $\rightarrow$ External Standard Integration (Using community benchmarks within the platform).</t>
   </si>
+  <si>
+    <t xml:space="preserve"> Sandboxing: Execution isolation for tool use.
+        2. Trajectory Observability: Immutable audit logs of agent plans and actions.
+        3. Safety Ontologies: Structured hazard analysis.
+        4. Role-Based Access Control (RBAC): Limiting agent permissions.</t>
+  </si>
+  <si>
+    <t>Holistic Pipeline QA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -939,12 +939,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -977,7 +971,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -987,13 +981,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1328,860 +1318,863 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13955A0-F322-4CC0-9DEF-340557280746}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="6.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="61.88671875" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="7" t="s">
+    </row>
+    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="7" t="s">
+    </row>
+    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2021</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="7">
-        <v>2021</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="J9" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="4">
+      <c r="C10" s="4">
         <v>2025</v>
       </c>
+      <c r="D10" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="E10" s="7" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="6">
-        <v>2023</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="J11" s="7" t="s">
+      <c r="J14" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="J19" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="6">
         <v>2025</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="D21" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="6">
         <v>2024</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="D23" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D20" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D21" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D22" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D23" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="J23" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
+      <c r="B24" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="C24" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="7">
-        <v>2024</v>
-      </c>
       <c r="E24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="J24" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+      <c r="B25" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="D25" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>258</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J25" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
+      <c r="B26" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="C26" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D26" s="7">
-        <v>2025</v>
-      </c>
       <c r="E26" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>162</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="J26" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
+      <c r="B27" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="C27" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="D27" s="7">
-        <v>2025</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>168</v>
@@ -2192,63 +2185,63 @@
       <c r="G27" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+      <c r="B28" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="C28" s="6">
+        <v>2020</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D28" s="7">
-        <v>2020</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>52</v>
-      </c>
       <c r="F28" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G28" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="J28" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K28" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
+      <c r="B29" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="D29" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>182</v>
@@ -2256,28 +2249,28 @@
       <c r="G29" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J29" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
+      <c r="B30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="C30" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="D30" s="7">
-        <v>2025</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>189</v>
@@ -2288,241 +2281,238 @@
       <c r="G30" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="K30" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
+      <c r="B31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="C31" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>196</v>
-      </c>
-      <c r="D31" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>257</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J31" s="7" t="s">
+      <c r="B32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B32" s="7" t="s">
+      <c r="E32" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D32" s="7">
+      <c r="F32" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C33" s="6">
         <v>2025</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="E33" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="D33" s="7">
+      <c r="G33" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" s="6">
         <v>2025</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
+      <c r="D34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="G34" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="D34" s="7">
+      <c r="H34" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C35" s="6">
+        <v>2022</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36" s="6">
         <v>2025</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D35" s="7">
-        <v>2022</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+      <c r="D36" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="F36" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D36" s="7">
-        <v>2025</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F36" s="7" t="s">
+      <c r="G36" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="H36" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="I36" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="J36" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="B37" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="K36" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+      <c r="C37" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="E37" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D37" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E37" s="7" t="s">
+      <c r="F37" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="G37" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H37" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="I37" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="H37" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>241</v>
+      <c r="J37" s="6" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
